--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252030</v>
+        <v>121252045</v>
       </c>
       <c r="B2" t="n">
-        <v>57348</v>
+        <v>91973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>780156</v>
+        <v>780443</v>
       </c>
       <c r="R2" t="n">
-        <v>7241427</v>
+        <v>7241811</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252042</v>
+        <v>121252037</v>
       </c>
       <c r="B3" t="n">
-        <v>90705</v>
+        <v>78338</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>780388</v>
+        <v>780297</v>
       </c>
       <c r="R3" t="n">
-        <v>7241696</v>
+        <v>7241876</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252034</v>
+        <v>121252041</v>
       </c>
       <c r="B4" t="n">
-        <v>57364</v>
+        <v>78337</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,42 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780223</v>
+        <v>780441</v>
       </c>
       <c r="R4" t="n">
-        <v>7241946</v>
+        <v>7241547</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252039</v>
+        <v>121252036</v>
       </c>
       <c r="B5" t="n">
-        <v>78335</v>
+        <v>79586</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1047,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780459</v>
+        <v>780412</v>
       </c>
       <c r="R5" t="n">
-        <v>7241605</v>
+        <v>7241695</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252033</v>
+        <v>121252032</v>
       </c>
       <c r="B6" t="n">
-        <v>57501</v>
+        <v>57351</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,34 +1099,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780312</v>
+        <v>780074</v>
       </c>
       <c r="R6" t="n">
-        <v>7241400</v>
+        <v>7241491</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252036</v>
+        <v>121252042</v>
       </c>
       <c r="B7" t="n">
-        <v>79583</v>
+        <v>90715</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,25 +1205,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780412</v>
+        <v>780388</v>
       </c>
       <c r="R7" t="n">
-        <v>7241695</v>
+        <v>7241696</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252043</v>
+        <v>121252033</v>
       </c>
       <c r="B8" t="n">
-        <v>82382</v>
+        <v>57504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,21 +1311,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1353,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780453</v>
+        <v>780312</v>
       </c>
       <c r="R8" t="n">
-        <v>7241681</v>
+        <v>7241400</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252029</v>
+        <v>121252035</v>
       </c>
       <c r="B9" t="n">
-        <v>90957</v>
+        <v>57367</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1427,30 +1409,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1458,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780314</v>
+        <v>780451</v>
       </c>
       <c r="R9" t="n">
-        <v>7241830</v>
+        <v>7241569</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,18 +1483,12 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ska mikroskoperas, men tycker det stämmer makroskopiskt med de karaktärer jag kunnat hitta i både bestämningslitteratur och råd från kunniga. Porerna går hela vägen ut i kanten, den är mjuk (kändes "fluffig" i färskt tillstånd och nu då den är torkad är den mycket spröd och blir snabbt till pulver om man rullar den mellan fingrarna. Upplever den inte alls seg.), fäster rätt hårt i underlaget men inte stenhårt, är ungefär 5mm tjock, 3-4 porer/mm (17-19/5mm) med enskilda större porer insprängda, på mycket grov kolad tallåga tätt tryckt mot marken. Området mycket tydligt präglad av brand, bränd silverved av tall i olika dimensioner fanns genomgående spritt i området.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1526,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121252045</v>
+        <v>121252043</v>
       </c>
       <c r="B10" t="n">
-        <v>91963</v>
+        <v>82385</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1538,25 +1519,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780443</v>
+        <v>780453</v>
       </c>
       <c r="R10" t="n">
-        <v>7241811</v>
+        <v>7241681</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121252040</v>
+        <v>121252039</v>
       </c>
       <c r="B11" t="n">
-        <v>78334</v>
+        <v>78338</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1625,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>780431</v>
+        <v>780459</v>
       </c>
       <c r="R11" t="n">
-        <v>7241554</v>
+        <v>7241605</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,10 +1711,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121252037</v>
+        <v>121252031</v>
       </c>
       <c r="B12" t="n">
-        <v>78335</v>
+        <v>57351</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,34 +1727,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780297</v>
+        <v>780129</v>
       </c>
       <c r="R12" t="n">
-        <v>7241876</v>
+        <v>7241443</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,6 +1795,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121252047</v>
+        <v>121252040</v>
       </c>
       <c r="B13" t="n">
-        <v>91963</v>
+        <v>78337</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1844,25 +1838,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780452</v>
+        <v>780431</v>
       </c>
       <c r="R13" t="n">
-        <v>7241612</v>
+        <v>7241554</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121252046</v>
+        <v>121252047</v>
       </c>
       <c r="B14" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1974,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780408</v>
+        <v>780452</v>
       </c>
       <c r="R14" t="n">
-        <v>7241743</v>
+        <v>7241612</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,10 +2030,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121252035</v>
+        <v>121252030</v>
       </c>
       <c r="B15" t="n">
-        <v>57364</v>
+        <v>57351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2052,16 +2046,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2084,10 +2078,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>780451</v>
+        <v>780156</v>
       </c>
       <c r="R15" t="n">
-        <v>7241569</v>
+        <v>7241427</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2120,6 +2114,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2146,10 +2145,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121252044</v>
+        <v>121252029</v>
       </c>
       <c r="B16" t="n">
-        <v>91963</v>
+        <v>90967</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2158,38 +2157,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>71</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>780241</v>
+        <v>780314</v>
       </c>
       <c r="R16" t="n">
-        <v>7241838</v>
+        <v>7241830</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2224,12 +2226,18 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ska mikroskoperas, men tycker det stämmer makroskopiskt med de karaktärer jag kunnat hitta i både bestämningslitteratur och råd från kunniga. Porerna går hela vägen ut i kanten, den är mjuk (kändes "fluffig" i färskt tillstånd och nu då den är torkad är den mycket spröd och blir snabbt till pulver om man rullar den mellan fingrarna. Upplever den inte alls seg.), fäster rätt hårt i underlaget men inte stenhårt, är ungefär 5mm tjock, 3-4 porer/mm (17-19/5mm) med enskilda större porer insprängda, på mycket grov kolad tallåga tätt tryckt mot marken. Området mycket tydligt präglad av brand, bränd silverved av tall i olika dimensioner fanns genomgående spritt i området.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2248,10 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121252031</v>
+        <v>121252034</v>
       </c>
       <c r="B17" t="n">
-        <v>57348</v>
+        <v>57367</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2264,16 +2272,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2296,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>780129</v>
+        <v>780223</v>
       </c>
       <c r="R17" t="n">
-        <v>7241443</v>
+        <v>7241946</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,7 +2344,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2363,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121252041</v>
+        <v>121252044</v>
       </c>
       <c r="B18" t="n">
-        <v>78334</v>
+        <v>91973</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2375,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2403,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780441</v>
+        <v>780241</v>
       </c>
       <c r="R18" t="n">
-        <v>7241547</v>
+        <v>7241838</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2465,10 +2473,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121252032</v>
+        <v>121252046</v>
       </c>
       <c r="B19" t="n">
-        <v>57348</v>
+        <v>91973</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2477,46 +2485,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>780074</v>
+        <v>780408</v>
       </c>
       <c r="R19" t="n">
-        <v>7241491</v>
+        <v>7241743</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -1507,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121252043</v>
+        <v>121252031</v>
       </c>
       <c r="B10" t="n">
-        <v>82385</v>
+        <v>57351</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,34 +1523,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780453</v>
+        <v>780129</v>
       </c>
       <c r="R10" t="n">
-        <v>7241681</v>
+        <v>7241443</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1583,6 +1591,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,10 +1724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121252031</v>
+        <v>121252043</v>
       </c>
       <c r="B12" t="n">
-        <v>57351</v>
+        <v>82385</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,42 +1740,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780129</v>
+        <v>780453</v>
       </c>
       <c r="R12" t="n">
-        <v>7241443</v>
+        <v>7241681</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,11 +1800,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252036</v>
+        <v>121252032</v>
       </c>
       <c r="B5" t="n">
-        <v>79586</v>
+        <v>57351</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780412</v>
+        <v>780074</v>
       </c>
       <c r="R5" t="n">
-        <v>7241695</v>
+        <v>7241491</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252032</v>
+        <v>121252036</v>
       </c>
       <c r="B6" t="n">
-        <v>57351</v>
+        <v>79586</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,46 +1103,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780074</v>
+        <v>780412</v>
       </c>
       <c r="R6" t="n">
-        <v>7241491</v>
+        <v>7241695</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1507,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121252031</v>
+        <v>121252043</v>
       </c>
       <c r="B10" t="n">
-        <v>57351</v>
+        <v>82385</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,42 +1523,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780129</v>
+        <v>780453</v>
       </c>
       <c r="R10" t="n">
-        <v>7241443</v>
+        <v>7241681</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,11 +1583,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,10 +1711,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121252043</v>
+        <v>121252031</v>
       </c>
       <c r="B12" t="n">
-        <v>82385</v>
+        <v>57351</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1740,34 +1727,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780453</v>
+        <v>780129</v>
       </c>
       <c r="R12" t="n">
-        <v>7241681</v>
+        <v>7241443</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,6 +1795,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252045</v>
+        <v>121252031</v>
       </c>
       <c r="B2" t="n">
-        <v>91973</v>
+        <v>57351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>780443</v>
+        <v>780129</v>
       </c>
       <c r="R2" t="n">
-        <v>7241811</v>
+        <v>7241443</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252037</v>
+        <v>121252036</v>
       </c>
       <c r="B3" t="n">
-        <v>78338</v>
+        <v>79586</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>780297</v>
+        <v>780412</v>
       </c>
       <c r="R3" t="n">
-        <v>7241876</v>
+        <v>7241695</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252041</v>
+        <v>121252043</v>
       </c>
       <c r="B4" t="n">
-        <v>78337</v>
+        <v>82385</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780441</v>
+        <v>780453</v>
       </c>
       <c r="R4" t="n">
-        <v>7241547</v>
+        <v>7241681</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252032</v>
+        <v>121252045</v>
       </c>
       <c r="B5" t="n">
-        <v>57351</v>
+        <v>91973</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,46 +1006,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780074</v>
+        <v>780443</v>
       </c>
       <c r="R5" t="n">
-        <v>7241491</v>
+        <v>7241811</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252036</v>
+        <v>121252029</v>
       </c>
       <c r="B6" t="n">
-        <v>79586</v>
+        <v>90967</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,38 +1108,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>71</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780412</v>
+        <v>780314</v>
       </c>
       <c r="R6" t="n">
-        <v>7241695</v>
+        <v>7241830</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,12 +1177,18 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ska mikroskoperas, men tycker det stämmer makroskopiskt med de karaktärer jag kunnat hitta i både bestämningslitteratur och råd från kunniga. Porerna går hela vägen ut i kanten, den är mjuk (kändes "fluffig" i färskt tillstånd och nu då den är torkad är den mycket spröd och blir snabbt till pulver om man rullar den mellan fingrarna. Upplever den inte alls seg.), fäster rätt hårt i underlaget men inte stenhårt, är ungefär 5mm tjock, 3-4 porer/mm (17-19/5mm) med enskilda större porer insprängda, på mycket grov kolad tallåga tätt tryckt mot marken. Området mycket tydligt präglad av brand, bränd silverved av tall i olika dimensioner fanns genomgående spritt i området.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1193,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252042</v>
+        <v>121252047</v>
       </c>
       <c r="B7" t="n">
-        <v>90715</v>
+        <v>91973</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,25 +1219,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780388</v>
+        <v>780452</v>
       </c>
       <c r="R7" t="n">
-        <v>7241696</v>
+        <v>7241612</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252033</v>
+        <v>121252034</v>
       </c>
       <c r="B8" t="n">
-        <v>57504</v>
+        <v>57367</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1311,34 +1325,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780312</v>
+        <v>780223</v>
       </c>
       <c r="R8" t="n">
-        <v>7241400</v>
+        <v>7241946</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,6 +1393,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252035</v>
+        <v>121252032</v>
       </c>
       <c r="B9" t="n">
-        <v>57367</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1413,16 +1440,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1435,7 +1462,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1445,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780451</v>
+        <v>780074</v>
       </c>
       <c r="R9" t="n">
-        <v>7241569</v>
+        <v>7241491</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121252043</v>
+        <v>121252039</v>
       </c>
       <c r="B10" t="n">
-        <v>82385</v>
+        <v>78338</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,21 +1550,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780453</v>
+        <v>780459</v>
       </c>
       <c r="R10" t="n">
-        <v>7241681</v>
+        <v>7241605</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121252039</v>
+        <v>121252046</v>
       </c>
       <c r="B11" t="n">
-        <v>78338</v>
+        <v>91973</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1621,25 +1648,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1649,10 +1676,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>780459</v>
+        <v>780408</v>
       </c>
       <c r="R11" t="n">
-        <v>7241605</v>
+        <v>7241743</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,10 +1738,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121252031</v>
+        <v>121252037</v>
       </c>
       <c r="B12" t="n">
-        <v>57351</v>
+        <v>78338</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,42 +1754,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780129</v>
+        <v>780297</v>
       </c>
       <c r="R12" t="n">
-        <v>7241443</v>
+        <v>7241876</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,11 +1814,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,10 +1942,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121252047</v>
+        <v>121252041</v>
       </c>
       <c r="B14" t="n">
-        <v>91973</v>
+        <v>78337</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,25 +1954,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1968,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780452</v>
+        <v>780441</v>
       </c>
       <c r="R14" t="n">
-        <v>7241612</v>
+        <v>7241547</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,10 +2044,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121252030</v>
+        <v>121252035</v>
       </c>
       <c r="B15" t="n">
-        <v>57351</v>
+        <v>57367</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2046,16 +2060,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2078,10 +2092,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>780156</v>
+        <v>780451</v>
       </c>
       <c r="R15" t="n">
-        <v>7241427</v>
+        <v>7241569</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2114,11 +2128,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2145,10 +2154,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121252029</v>
+        <v>121252033</v>
       </c>
       <c r="B16" t="n">
-        <v>90967</v>
+        <v>57504</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2157,41 +2166,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>71</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>780314</v>
+        <v>780312</v>
       </c>
       <c r="R16" t="n">
-        <v>7241830</v>
+        <v>7241400</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2226,18 +2232,12 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ska mikroskoperas, men tycker det stämmer makroskopiskt med de karaktärer jag kunnat hitta i både bestämningslitteratur och råd från kunniga. Porerna går hela vägen ut i kanten, den är mjuk (kändes "fluffig" i färskt tillstånd och nu då den är torkad är den mycket spröd och blir snabbt till pulver om man rullar den mellan fingrarna. Upplever den inte alls seg.), fäster rätt hårt i underlaget men inte stenhårt, är ungefär 5mm tjock, 3-4 porer/mm (17-19/5mm) med enskilda större porer insprängda, på mycket grov kolad tallåga tätt tryckt mot marken. Området mycket tydligt präglad av brand, bränd silverved av tall i olika dimensioner fanns genomgående spritt i området.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121252034</v>
+        <v>121252042</v>
       </c>
       <c r="B17" t="n">
-        <v>57367</v>
+        <v>90715</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2272,42 +2272,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>780223</v>
+        <v>780388</v>
       </c>
       <c r="R17" t="n">
-        <v>7241946</v>
+        <v>7241696</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,11 +2332,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2371,10 +2358,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121252044</v>
+        <v>121252030</v>
       </c>
       <c r="B18" t="n">
-        <v>91973</v>
+        <v>57351</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,38 +2370,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780241</v>
+        <v>780156</v>
       </c>
       <c r="R18" t="n">
-        <v>7241838</v>
+        <v>7241427</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,6 +2442,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2473,7 +2473,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121252046</v>
+        <v>121252044</v>
       </c>
       <c r="B19" t="n">
         <v>91973</v>
@@ -2513,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>780408</v>
+        <v>780241</v>
       </c>
       <c r="R19" t="n">
-        <v>7241743</v>
+        <v>7241838</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252036</v>
+        <v>121252043</v>
       </c>
       <c r="B3" t="n">
-        <v>79586</v>
+        <v>82385</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>780412</v>
+        <v>780453</v>
       </c>
       <c r="R3" t="n">
-        <v>7241695</v>
+        <v>7241681</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252043</v>
+        <v>121252036</v>
       </c>
       <c r="B4" t="n">
-        <v>82385</v>
+        <v>79586</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780453</v>
+        <v>780412</v>
       </c>
       <c r="R4" t="n">
-        <v>7241681</v>
+        <v>7241695</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1096,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252029</v>
+        <v>121252047</v>
       </c>
       <c r="B6" t="n">
-        <v>90967</v>
+        <v>91973</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,41 +1108,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>71</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780314</v>
+        <v>780452</v>
       </c>
       <c r="R6" t="n">
-        <v>7241830</v>
+        <v>7241612</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,18 +1174,12 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ska mikroskoperas, men tycker det stämmer makroskopiskt med de karaktärer jag kunnat hitta i både bestämningslitteratur och råd från kunniga. Porerna går hela vägen ut i kanten, den är mjuk (kändes "fluffig" i färskt tillstånd och nu då den är torkad är den mycket spröd och blir snabbt till pulver om man rullar den mellan fingrarna. Upplever den inte alls seg.), fäster rätt hårt i underlaget men inte stenhårt, är ungefär 5mm tjock, 3-4 porer/mm (17-19/5mm) med enskilda större porer insprängda, på mycket grov kolad tallåga tätt tryckt mot marken. Området mycket tydligt präglad av brand, bränd silverved av tall i olika dimensioner fanns genomgående spritt i området.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1207,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252047</v>
+        <v>121252034</v>
       </c>
       <c r="B7" t="n">
-        <v>91973</v>
+        <v>57367</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,38 +1210,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780452</v>
+        <v>780223</v>
       </c>
       <c r="R7" t="n">
-        <v>7241612</v>
+        <v>7241946</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,6 +1282,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252034</v>
+        <v>121252032</v>
       </c>
       <c r="B8" t="n">
-        <v>57367</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,16 +1329,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1347,7 +1351,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1357,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780223</v>
+        <v>780074</v>
       </c>
       <c r="R8" t="n">
-        <v>7241946</v>
+        <v>7241491</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,11 +1397,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252032</v>
+        <v>121252039</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>78338</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,42 +1439,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780074</v>
+        <v>780459</v>
       </c>
       <c r="R9" t="n">
-        <v>7241491</v>
+        <v>7241605</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121252039</v>
+        <v>121252046</v>
       </c>
       <c r="B10" t="n">
-        <v>78338</v>
+        <v>91973</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,25 +1537,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1574,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780459</v>
+        <v>780408</v>
       </c>
       <c r="R10" t="n">
-        <v>7241605</v>
+        <v>7241743</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121252046</v>
+        <v>121252037</v>
       </c>
       <c r="B11" t="n">
-        <v>91973</v>
+        <v>78338</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,25 +1639,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1676,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>780408</v>
+        <v>780297</v>
       </c>
       <c r="R11" t="n">
-        <v>7241743</v>
+        <v>7241876</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,10 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121252037</v>
+        <v>121252040</v>
       </c>
       <c r="B12" t="n">
-        <v>78338</v>
+        <v>78337</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1754,21 +1745,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,10 +1769,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780297</v>
+        <v>780431</v>
       </c>
       <c r="R12" t="n">
-        <v>7241876</v>
+        <v>7241554</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,7 +1831,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121252040</v>
+        <v>121252041</v>
       </c>
       <c r="B13" t="n">
         <v>78337</v>
@@ -1880,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780431</v>
+        <v>780441</v>
       </c>
       <c r="R13" t="n">
-        <v>7241554</v>
+        <v>7241547</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,10 +1933,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121252041</v>
+        <v>121252035</v>
       </c>
       <c r="B14" t="n">
-        <v>78337</v>
+        <v>57367</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1958,34 +1949,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780441</v>
+        <v>780451</v>
       </c>
       <c r="R14" t="n">
-        <v>7241547</v>
+        <v>7241569</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,10 +2043,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121252035</v>
+        <v>121252033</v>
       </c>
       <c r="B15" t="n">
-        <v>57367</v>
+        <v>57504</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2060,42 +2059,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>780451</v>
+        <v>780312</v>
       </c>
       <c r="R15" t="n">
-        <v>7241569</v>
+        <v>7241400</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2154,10 +2145,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121252033</v>
+        <v>121252042</v>
       </c>
       <c r="B16" t="n">
-        <v>57504</v>
+        <v>90715</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2170,21 +2161,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2194,10 +2185,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>780312</v>
+        <v>780388</v>
       </c>
       <c r="R16" t="n">
-        <v>7241400</v>
+        <v>7241696</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,10 +2247,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121252042</v>
+        <v>121252030</v>
       </c>
       <c r="B17" t="n">
-        <v>90715</v>
+        <v>57351</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2272,34 +2263,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>780388</v>
+        <v>780156</v>
       </c>
       <c r="R17" t="n">
-        <v>7241696</v>
+        <v>7241427</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,6 +2331,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2358,10 +2362,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121252030</v>
+        <v>121252044</v>
       </c>
       <c r="B18" t="n">
-        <v>57351</v>
+        <v>91973</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2370,46 +2374,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780156</v>
+        <v>780241</v>
       </c>
       <c r="R18" t="n">
-        <v>7241427</v>
+        <v>7241838</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,11 +2438,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2473,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121252044</v>
+        <v>121252029</v>
       </c>
       <c r="B19" t="n">
-        <v>91973</v>
+        <v>90967</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,38 +2476,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>71</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>780241</v>
+        <v>780314</v>
       </c>
       <c r="R19" t="n">
-        <v>7241838</v>
+        <v>7241830</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2551,11 +2545,21 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2024-12-04 Nu mikroskoperad av Mikael Gudrunsson, urskogsporing stämmer!  2024-11-17 Ska mikroskoperas, men tycker det stämmer makroskopiskt med de karaktärer jag kunnat hitta i både bestämningslitteratur och råd från kunniga. Porerna går hela vägen ut i kanten, den är mjuk (kändes "fluffig" i färskt tillstånd och nu då den är torkad är den mycket spröd och blir snabbt till pulver om man rullar den mellan fingrarna. Upplever den inte alls seg.), fäster rätt hårt i underlaget men inte stenhårt, är ungefär 5mm tjock, 3-4 porer/mm (17-19/5mm) med enskilda större porer insprängda, på mycket grov kolad tallåga tätt tryckt mot marken. Området mycket tydligt präglad av brand, bränd silverved av tall i olika dimensioner fanns genomgående spritt i området.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG19" t="b">
         <v>0</v>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252031</v>
+        <v>121252032</v>
       </c>
       <c r="B2" t="n">
         <v>57351</v>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>780129</v>
+        <v>780074</v>
       </c>
       <c r="R2" t="n">
-        <v>7241443</v>
+        <v>7241491</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,11 +759,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252043</v>
+        <v>121252036</v>
       </c>
       <c r="B3" t="n">
-        <v>82385</v>
+        <v>79589</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>780453</v>
+        <v>780412</v>
       </c>
       <c r="R3" t="n">
-        <v>7241681</v>
+        <v>7241695</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252036</v>
+        <v>121252033</v>
       </c>
       <c r="B4" t="n">
-        <v>79586</v>
+        <v>57504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780412</v>
+        <v>780312</v>
       </c>
       <c r="R4" t="n">
-        <v>7241695</v>
+        <v>7241400</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252045</v>
+        <v>121252035</v>
       </c>
       <c r="B5" t="n">
-        <v>91973</v>
+        <v>57367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,38 +1001,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780443</v>
+        <v>780451</v>
       </c>
       <c r="R5" t="n">
-        <v>7241811</v>
+        <v>7241569</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252047</v>
+        <v>121252034</v>
       </c>
       <c r="B6" t="n">
-        <v>91973</v>
+        <v>57367</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,38 +1111,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780452</v>
+        <v>780223</v>
       </c>
       <c r="R6" t="n">
-        <v>7241612</v>
+        <v>7241946</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,6 +1183,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252034</v>
+        <v>121252045</v>
       </c>
       <c r="B7" t="n">
-        <v>57367</v>
+        <v>91985</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,46 +1226,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780223</v>
+        <v>780443</v>
       </c>
       <c r="R7" t="n">
-        <v>7241946</v>
+        <v>7241811</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,11 +1290,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252032</v>
+        <v>121252044</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>91985</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,46 +1328,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780074</v>
+        <v>780241</v>
       </c>
       <c r="R8" t="n">
-        <v>7241491</v>
+        <v>7241838</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252039</v>
+        <v>121252031</v>
       </c>
       <c r="B9" t="n">
-        <v>78338</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,34 +1434,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780459</v>
+        <v>780129</v>
       </c>
       <c r="R9" t="n">
-        <v>7241605</v>
+        <v>7241443</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,6 +1502,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1525,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121252046</v>
+        <v>121252037</v>
       </c>
       <c r="B10" t="n">
-        <v>91973</v>
+        <v>78341</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,25 +1545,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1565,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780408</v>
+        <v>780297</v>
       </c>
       <c r="R10" t="n">
-        <v>7241743</v>
+        <v>7241876</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,10 +1635,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121252037</v>
+        <v>121252047</v>
       </c>
       <c r="B11" t="n">
-        <v>78338</v>
+        <v>91985</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,25 +1647,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1667,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>780297</v>
+        <v>780452</v>
       </c>
       <c r="R11" t="n">
-        <v>7241876</v>
+        <v>7241612</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121252040</v>
+        <v>121252046</v>
       </c>
       <c r="B12" t="n">
-        <v>78337</v>
+        <v>91985</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,25 +1749,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1769,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780431</v>
+        <v>780408</v>
       </c>
       <c r="R12" t="n">
-        <v>7241554</v>
+        <v>7241743</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,10 +1839,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121252041</v>
+        <v>121252043</v>
       </c>
       <c r="B13" t="n">
-        <v>78337</v>
+        <v>82388</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1847,21 +1855,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1871,10 +1879,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780441</v>
+        <v>780453</v>
       </c>
       <c r="R13" t="n">
-        <v>7241547</v>
+        <v>7241681</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,10 +1941,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121252035</v>
+        <v>121252040</v>
       </c>
       <c r="B14" t="n">
-        <v>57367</v>
+        <v>78340</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1949,42 +1957,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780451</v>
+        <v>780431</v>
       </c>
       <c r="R14" t="n">
-        <v>7241569</v>
+        <v>7241554</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121252033</v>
+        <v>121252041</v>
       </c>
       <c r="B15" t="n">
-        <v>57504</v>
+        <v>78340</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>780312</v>
+        <v>780441</v>
       </c>
       <c r="R15" t="n">
-        <v>7241400</v>
+        <v>7241547</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121252042</v>
+        <v>121252039</v>
       </c>
       <c r="B16" t="n">
-        <v>90715</v>
+        <v>78341</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2161,21 +2161,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>780388</v>
+        <v>780459</v>
       </c>
       <c r="R16" t="n">
-        <v>7241696</v>
+        <v>7241605</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,10 +2362,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121252044</v>
+        <v>121252042</v>
       </c>
       <c r="B18" t="n">
-        <v>91973</v>
+        <v>90727</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2374,25 +2374,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780241</v>
+        <v>780388</v>
       </c>
       <c r="R18" t="n">
-        <v>7241838</v>
+        <v>7241696</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
         <v>121252029</v>
       </c>
       <c r="B19" t="n">
-        <v>90967</v>
+        <v>90979</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252032</v>
+        <v>121252044</v>
       </c>
       <c r="B2" t="n">
-        <v>57351</v>
+        <v>91986</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>780074</v>
+        <v>780241</v>
       </c>
       <c r="R2" t="n">
-        <v>7241491</v>
+        <v>7241838</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252036</v>
+        <v>121252047</v>
       </c>
       <c r="B3" t="n">
-        <v>79589</v>
+        <v>91986</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>780412</v>
+        <v>780452</v>
       </c>
       <c r="R3" t="n">
-        <v>7241695</v>
+        <v>7241612</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252033</v>
+        <v>121252042</v>
       </c>
       <c r="B4" t="n">
-        <v>57504</v>
+        <v>90728</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780312</v>
+        <v>780388</v>
       </c>
       <c r="R4" t="n">
-        <v>7241400</v>
+        <v>7241696</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252035</v>
+        <v>121252032</v>
       </c>
       <c r="B5" t="n">
-        <v>57367</v>
+        <v>57351</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,16 +997,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1027,7 +1019,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1037,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780451</v>
+        <v>780074</v>
       </c>
       <c r="R5" t="n">
-        <v>7241569</v>
+        <v>7241491</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1214,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252045</v>
+        <v>121252033</v>
       </c>
       <c r="B7" t="n">
-        <v>91985</v>
+        <v>57504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,25 +1218,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1254,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780443</v>
+        <v>780312</v>
       </c>
       <c r="R7" t="n">
-        <v>7241811</v>
+        <v>7241400</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1308,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252044</v>
+        <v>121252030</v>
       </c>
       <c r="B8" t="n">
-        <v>91985</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,38 +1320,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780241</v>
+        <v>780156</v>
       </c>
       <c r="R8" t="n">
-        <v>7241838</v>
+        <v>7241427</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,6 +1392,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1418,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252031</v>
+        <v>121252043</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>82388</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,42 +1439,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780129</v>
+        <v>780453</v>
       </c>
       <c r="R9" t="n">
-        <v>7241443</v>
+        <v>7241681</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,11 +1499,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121252037</v>
+        <v>121252045</v>
       </c>
       <c r="B10" t="n">
-        <v>78341</v>
+        <v>91986</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,25 +1537,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780297</v>
+        <v>780443</v>
       </c>
       <c r="R10" t="n">
-        <v>7241876</v>
+        <v>7241811</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121252047</v>
+        <v>121252035</v>
       </c>
       <c r="B11" t="n">
-        <v>91985</v>
+        <v>57367</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,38 +1639,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>780452</v>
+        <v>780451</v>
       </c>
       <c r="R11" t="n">
-        <v>7241612</v>
+        <v>7241569</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121252046</v>
+        <v>121252039</v>
       </c>
       <c r="B12" t="n">
-        <v>91985</v>
+        <v>78341</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1749,25 +1749,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780408</v>
+        <v>780459</v>
       </c>
       <c r="R12" t="n">
-        <v>7241743</v>
+        <v>7241605</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121252043</v>
+        <v>121252040</v>
       </c>
       <c r="B13" t="n">
-        <v>82388</v>
+        <v>78340</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780453</v>
+        <v>780431</v>
       </c>
       <c r="R13" t="n">
-        <v>7241681</v>
+        <v>7241554</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121252040</v>
+        <v>121252036</v>
       </c>
       <c r="B14" t="n">
-        <v>78340</v>
+        <v>79589</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1953,25 +1953,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780431</v>
+        <v>780412</v>
       </c>
       <c r="R14" t="n">
-        <v>7241554</v>
+        <v>7241695</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121252041</v>
+        <v>121252031</v>
       </c>
       <c r="B15" t="n">
-        <v>78340</v>
+        <v>57351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2059,34 +2059,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>780441</v>
+        <v>780129</v>
       </c>
       <c r="R15" t="n">
-        <v>7241547</v>
+        <v>7241443</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2119,6 +2127,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2145,7 +2158,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121252039</v>
+        <v>121252037</v>
       </c>
       <c r="B16" t="n">
         <v>78341</v>
@@ -2185,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>780459</v>
+        <v>780297</v>
       </c>
       <c r="R16" t="n">
-        <v>7241605</v>
+        <v>7241876</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2247,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121252030</v>
+        <v>121252041</v>
       </c>
       <c r="B17" t="n">
-        <v>57351</v>
+        <v>78340</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,42 +2276,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>780156</v>
+        <v>780441</v>
       </c>
       <c r="R17" t="n">
-        <v>7241427</v>
+        <v>7241547</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,11 +2336,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2362,10 +2362,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121252042</v>
+        <v>121252046</v>
       </c>
       <c r="B18" t="n">
-        <v>90727</v>
+        <v>91986</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2374,25 +2374,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780388</v>
+        <v>780408</v>
       </c>
       <c r="R18" t="n">
-        <v>7241696</v>
+        <v>7241743</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
         <v>121252029</v>
       </c>
       <c r="B19" t="n">
-        <v>90979</v>
+        <v>90980</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252044</v>
+        <v>121252031</v>
       </c>
       <c r="B2" t="n">
-        <v>91986</v>
+        <v>57354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>780241</v>
+        <v>780129</v>
       </c>
       <c r="R2" t="n">
-        <v>7241838</v>
+        <v>7241443</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252047</v>
+        <v>121252042</v>
       </c>
       <c r="B3" t="n">
-        <v>91986</v>
+        <v>90731</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>780452</v>
+        <v>780388</v>
       </c>
       <c r="R3" t="n">
-        <v>7241612</v>
+        <v>7241696</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252042</v>
+        <v>121252043</v>
       </c>
       <c r="B4" t="n">
-        <v>90728</v>
+        <v>82391</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780388</v>
+        <v>780453</v>
       </c>
       <c r="R4" t="n">
-        <v>7241696</v>
+        <v>7241681</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252032</v>
+        <v>121252039</v>
       </c>
       <c r="B5" t="n">
-        <v>57351</v>
+        <v>78344</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,42 +1010,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780074</v>
+        <v>780459</v>
       </c>
       <c r="R5" t="n">
-        <v>7241491</v>
+        <v>7241605</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252034</v>
+        <v>121252033</v>
       </c>
       <c r="B6" t="n">
-        <v>57367</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1107,42 +1112,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780223</v>
+        <v>780312</v>
       </c>
       <c r="R6" t="n">
-        <v>7241946</v>
+        <v>7241400</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,11 +1172,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252033</v>
+        <v>121252044</v>
       </c>
       <c r="B7" t="n">
-        <v>57504</v>
+        <v>91989</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,25 +1210,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780312</v>
+        <v>780241</v>
       </c>
       <c r="R7" t="n">
-        <v>7241400</v>
+        <v>7241838</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,10 +1300,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252030</v>
+        <v>121252034</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>57370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,16 +1316,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1356,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780156</v>
+        <v>780223</v>
       </c>
       <c r="R8" t="n">
-        <v>7241427</v>
+        <v>7241946</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,7 +1388,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252043</v>
+        <v>121252036</v>
       </c>
       <c r="B9" t="n">
-        <v>82388</v>
+        <v>79592</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,25 +1427,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1463,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780453</v>
+        <v>780412</v>
       </c>
       <c r="R9" t="n">
-        <v>7241681</v>
+        <v>7241695</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121252045</v>
+        <v>121252047</v>
       </c>
       <c r="B10" t="n">
-        <v>91986</v>
+        <v>91989</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1565,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780443</v>
+        <v>780452</v>
       </c>
       <c r="R10" t="n">
-        <v>7241811</v>
+        <v>7241612</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121252035</v>
+        <v>121252040</v>
       </c>
       <c r="B11" t="n">
-        <v>57367</v>
+        <v>78343</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1643,42 +1635,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>780451</v>
+        <v>780431</v>
       </c>
       <c r="R11" t="n">
-        <v>7241569</v>
+        <v>7241554</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,10 +1721,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121252039</v>
+        <v>121252045</v>
       </c>
       <c r="B12" t="n">
-        <v>78341</v>
+        <v>91989</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1749,25 +1733,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1761,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780459</v>
+        <v>780443</v>
       </c>
       <c r="R12" t="n">
-        <v>7241605</v>
+        <v>7241811</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,10 +1823,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121252040</v>
+        <v>121252030</v>
       </c>
       <c r="B13" t="n">
-        <v>78340</v>
+        <v>57354</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1855,34 +1839,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780431</v>
+        <v>780156</v>
       </c>
       <c r="R13" t="n">
-        <v>7241554</v>
+        <v>7241427</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,6 +1907,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1941,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121252036</v>
+        <v>121252037</v>
       </c>
       <c r="B14" t="n">
-        <v>79589</v>
+        <v>78344</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1953,25 +1950,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1981,10 +1978,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780412</v>
+        <v>780297</v>
       </c>
       <c r="R14" t="n">
-        <v>7241695</v>
+        <v>7241876</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2043,10 +2040,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121252031</v>
+        <v>121252032</v>
       </c>
       <c r="B15" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2081,7 +2078,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2091,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>780129</v>
+        <v>780074</v>
       </c>
       <c r="R15" t="n">
-        <v>7241443</v>
+        <v>7241491</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,11 +2124,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,10 +2150,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121252037</v>
+        <v>121252041</v>
       </c>
       <c r="B16" t="n">
-        <v>78341</v>
+        <v>78343</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2174,21 +2166,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2190,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>780297</v>
+        <v>780441</v>
       </c>
       <c r="R16" t="n">
-        <v>7241876</v>
+        <v>7241547</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,10 +2252,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121252041</v>
+        <v>121252035</v>
       </c>
       <c r="B17" t="n">
-        <v>78340</v>
+        <v>57370</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2276,34 +2268,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>780441</v>
+        <v>780451</v>
       </c>
       <c r="R17" t="n">
-        <v>7241547</v>
+        <v>7241569</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2365,7 @@
         <v>121252046</v>
       </c>
       <c r="B18" t="n">
-        <v>91986</v>
+        <v>91989</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>121252029</v>
       </c>
       <c r="B19" t="n">
-        <v>90980</v>
+        <v>90983</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252031</v>
+        <v>121252037</v>
       </c>
       <c r="B2" t="n">
-        <v>57354</v>
+        <v>78344</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>780129</v>
+        <v>780297</v>
       </c>
       <c r="R2" t="n">
-        <v>7241443</v>
+        <v>7241876</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252042</v>
+        <v>121252035</v>
       </c>
       <c r="B3" t="n">
-        <v>90731</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>780388</v>
+        <v>780451</v>
       </c>
       <c r="R3" t="n">
-        <v>7241696</v>
+        <v>7241569</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252043</v>
+        <v>121252045</v>
       </c>
       <c r="B4" t="n">
-        <v>82391</v>
+        <v>91989</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780453</v>
+        <v>780443</v>
       </c>
       <c r="R4" t="n">
-        <v>7241681</v>
+        <v>7241811</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1198,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252044</v>
+        <v>121252042</v>
       </c>
       <c r="B7" t="n">
-        <v>91989</v>
+        <v>90731</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,25 +1205,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780241</v>
+        <v>780388</v>
       </c>
       <c r="R7" t="n">
-        <v>7241838</v>
+        <v>7241696</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252034</v>
+        <v>121252041</v>
       </c>
       <c r="B8" t="n">
-        <v>57370</v>
+        <v>78343</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1316,42 +1311,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780223</v>
+        <v>780441</v>
       </c>
       <c r="R8" t="n">
-        <v>7241946</v>
+        <v>7241547</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,11 +1371,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121252047</v>
+        <v>121252040</v>
       </c>
       <c r="B10" t="n">
-        <v>91989</v>
+        <v>78343</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1529,25 +1511,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1557,10 +1539,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780452</v>
+        <v>780431</v>
       </c>
       <c r="R10" t="n">
-        <v>7241612</v>
+        <v>7241554</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,10 +1601,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121252040</v>
+        <v>121252044</v>
       </c>
       <c r="B11" t="n">
-        <v>78343</v>
+        <v>91989</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1631,25 +1613,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1659,10 +1641,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>780431</v>
+        <v>780241</v>
       </c>
       <c r="R11" t="n">
-        <v>7241554</v>
+        <v>7241838</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1721,10 +1703,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121252045</v>
+        <v>121252034</v>
       </c>
       <c r="B12" t="n">
-        <v>91989</v>
+        <v>57370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1733,38 +1715,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780443</v>
+        <v>780223</v>
       </c>
       <c r="R12" t="n">
-        <v>7241811</v>
+        <v>7241946</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,6 +1787,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1823,10 +1818,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121252030</v>
+        <v>121252047</v>
       </c>
       <c r="B13" t="n">
-        <v>57354</v>
+        <v>91989</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1835,46 +1830,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780156</v>
+        <v>780452</v>
       </c>
       <c r="R13" t="n">
-        <v>7241427</v>
+        <v>7241612</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1907,11 +1894,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1938,10 +1920,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121252037</v>
+        <v>121252046</v>
       </c>
       <c r="B14" t="n">
-        <v>78344</v>
+        <v>91989</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,25 +1932,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1978,10 +1960,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780297</v>
+        <v>780408</v>
       </c>
       <c r="R14" t="n">
-        <v>7241876</v>
+        <v>7241743</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2040,7 +2022,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121252032</v>
+        <v>121252031</v>
       </c>
       <c r="B15" t="n">
         <v>57354</v>
@@ -2078,7 +2060,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2088,10 +2070,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>780074</v>
+        <v>780129</v>
       </c>
       <c r="R15" t="n">
-        <v>7241491</v>
+        <v>7241443</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,6 +2106,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2150,10 +2137,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121252041</v>
+        <v>121252030</v>
       </c>
       <c r="B16" t="n">
-        <v>78343</v>
+        <v>57354</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2166,34 +2153,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>780441</v>
+        <v>780156</v>
       </c>
       <c r="R16" t="n">
-        <v>7241547</v>
+        <v>7241427</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2226,6 +2221,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2252,10 +2252,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121252035</v>
+        <v>121252043</v>
       </c>
       <c r="B17" t="n">
-        <v>57370</v>
+        <v>82391</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2268,42 +2268,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>780451</v>
+        <v>780453</v>
       </c>
       <c r="R17" t="n">
-        <v>7241569</v>
+        <v>7241681</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2362,10 +2354,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121252046</v>
+        <v>121252032</v>
       </c>
       <c r="B18" t="n">
-        <v>91989</v>
+        <v>57354</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2374,38 +2366,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780408</v>
+        <v>780074</v>
       </c>
       <c r="R18" t="n">
-        <v>7241743</v>
+        <v>7241491</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252045</v>
+        <v>121252039</v>
       </c>
       <c r="B4" t="n">
-        <v>91989</v>
+        <v>78344</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780443</v>
+        <v>780459</v>
       </c>
       <c r="R4" t="n">
-        <v>7241811</v>
+        <v>7241605</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252039</v>
+        <v>121252042</v>
       </c>
       <c r="B5" t="n">
-        <v>78344</v>
+        <v>90731</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780459</v>
+        <v>780388</v>
       </c>
       <c r="R5" t="n">
-        <v>7241605</v>
+        <v>7241696</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252033</v>
+        <v>121252045</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>91989</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,25 +1103,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780312</v>
+        <v>780443</v>
       </c>
       <c r="R6" t="n">
-        <v>7241400</v>
+        <v>7241811</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252042</v>
+        <v>121252033</v>
       </c>
       <c r="B7" t="n">
-        <v>90731</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1209,21 +1209,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780388</v>
+        <v>780312</v>
       </c>
       <c r="R7" t="n">
-        <v>7241696</v>
+        <v>7241400</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252037</v>
+        <v>121252030</v>
       </c>
       <c r="B2" t="n">
-        <v>78344</v>
+        <v>57355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>780297</v>
+        <v>780156</v>
       </c>
       <c r="R2" t="n">
-        <v>7241876</v>
+        <v>7241427</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252035</v>
+        <v>121252036</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>79593</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,46 +802,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>780451</v>
+        <v>780412</v>
       </c>
       <c r="R3" t="n">
-        <v>7241569</v>
+        <v>7241695</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252039</v>
+        <v>121252042</v>
       </c>
       <c r="B4" t="n">
-        <v>78344</v>
+        <v>90737</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780459</v>
+        <v>780388</v>
       </c>
       <c r="R4" t="n">
-        <v>7241605</v>
+        <v>7241696</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252042</v>
+        <v>121252039</v>
       </c>
       <c r="B5" t="n">
-        <v>90731</v>
+        <v>78345</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780388</v>
+        <v>780459</v>
       </c>
       <c r="R5" t="n">
-        <v>7241696</v>
+        <v>7241605</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1099,7 @@
         <v>121252045</v>
       </c>
       <c r="B6" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1193,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252033</v>
+        <v>121252035</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>57371</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1209,34 +1214,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780312</v>
+        <v>780451</v>
       </c>
       <c r="R7" t="n">
-        <v>7241400</v>
+        <v>7241569</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,10 +1308,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252041</v>
+        <v>121252044</v>
       </c>
       <c r="B8" t="n">
-        <v>78343</v>
+        <v>91995</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1307,25 +1320,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1335,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780441</v>
+        <v>780241</v>
       </c>
       <c r="R8" t="n">
-        <v>7241547</v>
+        <v>7241838</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,10 +1410,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252036</v>
+        <v>121252034</v>
       </c>
       <c r="B9" t="n">
-        <v>79592</v>
+        <v>57371</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,38 +1422,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780412</v>
+        <v>780223</v>
       </c>
       <c r="R9" t="n">
-        <v>7241695</v>
+        <v>7241946</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,6 +1494,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121252040</v>
+        <v>121252031</v>
       </c>
       <c r="B10" t="n">
-        <v>78343</v>
+        <v>57355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1515,34 +1541,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780431</v>
+        <v>780129</v>
       </c>
       <c r="R10" t="n">
-        <v>7241554</v>
+        <v>7241443</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,6 +1609,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121252044</v>
+        <v>121252033</v>
       </c>
       <c r="B11" t="n">
-        <v>91989</v>
+        <v>57508</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1613,25 +1652,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1641,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>780241</v>
+        <v>780312</v>
       </c>
       <c r="R11" t="n">
-        <v>7241838</v>
+        <v>7241400</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,10 +1742,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121252034</v>
+        <v>121252032</v>
       </c>
       <c r="B12" t="n">
-        <v>57370</v>
+        <v>57355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1719,16 +1758,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1741,7 +1780,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1751,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780223</v>
+        <v>780074</v>
       </c>
       <c r="R12" t="n">
-        <v>7241946</v>
+        <v>7241491</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,11 +1826,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1818,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121252047</v>
+        <v>121252041</v>
       </c>
       <c r="B13" t="n">
-        <v>91989</v>
+        <v>78344</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1830,25 +1864,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1858,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780452</v>
+        <v>780441</v>
       </c>
       <c r="R13" t="n">
-        <v>7241612</v>
+        <v>7241547</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,7 +1957,7 @@
         <v>121252046</v>
       </c>
       <c r="B14" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2022,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121252031</v>
+        <v>121252040</v>
       </c>
       <c r="B15" t="n">
-        <v>57354</v>
+        <v>78344</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2038,42 +2072,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>780129</v>
+        <v>780431</v>
       </c>
       <c r="R15" t="n">
-        <v>7241443</v>
+        <v>7241554</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2106,11 +2132,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2137,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121252030</v>
+        <v>121252043</v>
       </c>
       <c r="B16" t="n">
-        <v>57354</v>
+        <v>82392</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2153,42 +2174,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>780156</v>
+        <v>780453</v>
       </c>
       <c r="R16" t="n">
-        <v>7241427</v>
+        <v>7241681</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2221,11 +2234,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2252,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121252043</v>
+        <v>121252037</v>
       </c>
       <c r="B17" t="n">
-        <v>82391</v>
+        <v>78345</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2268,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2292,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>780453</v>
+        <v>780297</v>
       </c>
       <c r="R17" t="n">
-        <v>7241681</v>
+        <v>7241876</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2354,10 +2362,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121252032</v>
+        <v>121252047</v>
       </c>
       <c r="B18" t="n">
-        <v>57354</v>
+        <v>91995</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2366,46 +2374,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780074</v>
+        <v>780452</v>
       </c>
       <c r="R18" t="n">
-        <v>7241491</v>
+        <v>7241612</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
         <v>121252029</v>
       </c>
       <c r="B19" t="n">
-        <v>90983</v>
+        <v>90989</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252030</v>
+        <v>121252035</v>
       </c>
       <c r="B2" t="n">
-        <v>57355</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>780156</v>
+        <v>780451</v>
       </c>
       <c r="R2" t="n">
-        <v>7241427</v>
+        <v>7241569</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,11 +759,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,7 +788,7 @@
         <v>121252036</v>
       </c>
       <c r="B3" t="n">
-        <v>79593</v>
+        <v>79594</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252042</v>
+        <v>121252034</v>
       </c>
       <c r="B4" t="n">
-        <v>90737</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,34 +903,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780388</v>
+        <v>780223</v>
       </c>
       <c r="R4" t="n">
-        <v>7241696</v>
+        <v>7241946</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,6 +971,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252039</v>
+        <v>121252033</v>
       </c>
       <c r="B5" t="n">
-        <v>78345</v>
+        <v>57509</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780459</v>
+        <v>780312</v>
       </c>
       <c r="R5" t="n">
-        <v>7241605</v>
+        <v>7241400</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252045</v>
+        <v>121252047</v>
       </c>
       <c r="B6" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780443</v>
+        <v>780452</v>
       </c>
       <c r="R6" t="n">
-        <v>7241811</v>
+        <v>7241612</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252035</v>
+        <v>121252041</v>
       </c>
       <c r="B7" t="n">
-        <v>57371</v>
+        <v>78345</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1214,42 +1222,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780451</v>
+        <v>780441</v>
       </c>
       <c r="R7" t="n">
-        <v>7241569</v>
+        <v>7241547</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,10 +1308,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252044</v>
+        <v>121252039</v>
       </c>
       <c r="B8" t="n">
-        <v>91995</v>
+        <v>78346</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1320,25 +1320,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780241</v>
+        <v>780459</v>
       </c>
       <c r="R8" t="n">
-        <v>7241838</v>
+        <v>7241605</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,10 +1410,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252034</v>
+        <v>121252044</v>
       </c>
       <c r="B9" t="n">
-        <v>57371</v>
+        <v>91996</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1422,46 +1422,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780223</v>
+        <v>780241</v>
       </c>
       <c r="R9" t="n">
-        <v>7241946</v>
+        <v>7241838</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,11 +1486,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1525,10 +1512,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121252031</v>
+        <v>121252040</v>
       </c>
       <c r="B10" t="n">
-        <v>57355</v>
+        <v>78345</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,42 +1528,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780129</v>
+        <v>780431</v>
       </c>
       <c r="R10" t="n">
-        <v>7241443</v>
+        <v>7241554</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,11 +1588,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,10 +1614,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121252033</v>
+        <v>121252037</v>
       </c>
       <c r="B11" t="n">
-        <v>57508</v>
+        <v>78346</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,21 +1630,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1680,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>780312</v>
+        <v>780297</v>
       </c>
       <c r="R11" t="n">
-        <v>7241400</v>
+        <v>7241876</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,10 +1716,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121252032</v>
+        <v>121252045</v>
       </c>
       <c r="B12" t="n">
-        <v>57355</v>
+        <v>91996</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1754,46 +1728,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780074</v>
+        <v>780443</v>
       </c>
       <c r="R12" t="n">
-        <v>7241491</v>
+        <v>7241811</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,10 +1818,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121252041</v>
+        <v>121252032</v>
       </c>
       <c r="B13" t="n">
-        <v>78344</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,34 +1834,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780441</v>
+        <v>780074</v>
       </c>
       <c r="R13" t="n">
-        <v>7241547</v>
+        <v>7241491</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1954,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121252046</v>
+        <v>121252043</v>
       </c>
       <c r="B14" t="n">
-        <v>91995</v>
+        <v>82393</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1966,25 +1940,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780408</v>
+        <v>780453</v>
       </c>
       <c r="R14" t="n">
-        <v>7241743</v>
+        <v>7241681</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,10 +2030,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121252040</v>
+        <v>121252030</v>
       </c>
       <c r="B15" t="n">
-        <v>78344</v>
+        <v>57356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,34 +2046,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>780431</v>
+        <v>780156</v>
       </c>
       <c r="R15" t="n">
-        <v>7241554</v>
+        <v>7241427</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,6 +2114,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,10 +2145,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121252043</v>
+        <v>121252031</v>
       </c>
       <c r="B16" t="n">
-        <v>82392</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2174,34 +2161,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>780453</v>
+        <v>780129</v>
       </c>
       <c r="R16" t="n">
-        <v>7241681</v>
+        <v>7241443</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,6 +2229,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121252037</v>
+        <v>121252042</v>
       </c>
       <c r="B17" t="n">
-        <v>78345</v>
+        <v>90738</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2276,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>780297</v>
+        <v>780388</v>
       </c>
       <c r="R17" t="n">
-        <v>7241876</v>
+        <v>7241696</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2362,10 +2362,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121252047</v>
+        <v>121252046</v>
       </c>
       <c r="B18" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780452</v>
+        <v>780408</v>
       </c>
       <c r="R18" t="n">
-        <v>7241612</v>
+        <v>7241743</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2467,7 @@
         <v>121252029</v>
       </c>
       <c r="B19" t="n">
-        <v>90989</v>
+        <v>90990</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252035</v>
+        <v>121252031</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>780451</v>
+        <v>780129</v>
       </c>
       <c r="R2" t="n">
-        <v>7241569</v>
+        <v>7241443</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252034</v>
+        <v>121252047</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>91996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,46 +904,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780223</v>
+        <v>780452</v>
       </c>
       <c r="R4" t="n">
-        <v>7241946</v>
+        <v>7241612</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,11 +968,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252033</v>
+        <v>121252037</v>
       </c>
       <c r="B5" t="n">
-        <v>57509</v>
+        <v>78346</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,21 +1010,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1042,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780312</v>
+        <v>780297</v>
       </c>
       <c r="R5" t="n">
-        <v>7241400</v>
+        <v>7241876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252047</v>
+        <v>121252035</v>
       </c>
       <c r="B6" t="n">
-        <v>91996</v>
+        <v>57372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,38 +1108,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780452</v>
+        <v>780451</v>
       </c>
       <c r="R6" t="n">
-        <v>7241612</v>
+        <v>7241569</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252041</v>
+        <v>121252032</v>
       </c>
       <c r="B7" t="n">
-        <v>78345</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,34 +1222,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780441</v>
+        <v>780074</v>
       </c>
       <c r="R7" t="n">
-        <v>7241547</v>
+        <v>7241491</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252039</v>
+        <v>121252033</v>
       </c>
       <c r="B8" t="n">
-        <v>78346</v>
+        <v>57509</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1348,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780459</v>
+        <v>780312</v>
       </c>
       <c r="R8" t="n">
-        <v>7241605</v>
+        <v>7241400</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252044</v>
+        <v>121252030</v>
       </c>
       <c r="B9" t="n">
-        <v>91996</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1422,38 +1430,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780241</v>
+        <v>780156</v>
       </c>
       <c r="R9" t="n">
-        <v>7241838</v>
+        <v>7241427</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1486,6 +1502,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1512,7 +1533,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121252040</v>
+        <v>121252041</v>
       </c>
       <c r="B10" t="n">
         <v>78345</v>
@@ -1552,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780431</v>
+        <v>780441</v>
       </c>
       <c r="R10" t="n">
-        <v>7241554</v>
+        <v>7241547</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1614,10 +1635,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121252037</v>
+        <v>121252040</v>
       </c>
       <c r="B11" t="n">
-        <v>78346</v>
+        <v>78345</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,21 +1651,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1654,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>780297</v>
+        <v>780431</v>
       </c>
       <c r="R11" t="n">
-        <v>7241876</v>
+        <v>7241554</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1716,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121252045</v>
+        <v>121252042</v>
       </c>
       <c r="B12" t="n">
-        <v>91996</v>
+        <v>90738</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1728,25 +1749,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1756,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780443</v>
+        <v>780388</v>
       </c>
       <c r="R12" t="n">
-        <v>7241811</v>
+        <v>7241696</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,10 +1839,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121252032</v>
+        <v>121252046</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>91996</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1830,46 +1851,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780074</v>
+        <v>780408</v>
       </c>
       <c r="R13" t="n">
-        <v>7241491</v>
+        <v>7241743</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,10 +1941,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121252043</v>
+        <v>121252039</v>
       </c>
       <c r="B14" t="n">
-        <v>82393</v>
+        <v>78346</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1944,21 +1957,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1968,10 +1981,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780453</v>
+        <v>780459</v>
       </c>
       <c r="R14" t="n">
-        <v>7241681</v>
+        <v>7241605</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,10 +2043,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121252030</v>
+        <v>121252043</v>
       </c>
       <c r="B15" t="n">
-        <v>57356</v>
+        <v>82393</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2046,42 +2059,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>780156</v>
+        <v>780453</v>
       </c>
       <c r="R15" t="n">
-        <v>7241427</v>
+        <v>7241681</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2114,11 +2119,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2145,10 +2145,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121252031</v>
+        <v>121252044</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>91996</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2157,46 +2157,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>780129</v>
+        <v>780241</v>
       </c>
       <c r="R16" t="n">
-        <v>7241443</v>
+        <v>7241838</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,11 +2221,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,10 +2247,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121252042</v>
+        <v>121252034</v>
       </c>
       <c r="B17" t="n">
-        <v>90738</v>
+        <v>57372</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2276,34 +2263,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>780388</v>
+        <v>780223</v>
       </c>
       <c r="R17" t="n">
-        <v>7241696</v>
+        <v>7241946</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,6 +2331,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2362,7 +2362,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121252046</v>
+        <v>121252045</v>
       </c>
       <c r="B18" t="n">
         <v>91996</v>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780408</v>
+        <v>780443</v>
       </c>
       <c r="R18" t="n">
-        <v>7241743</v>
+        <v>7241811</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252031</v>
+        <v>121252036</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>79594</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>780129</v>
+        <v>780412</v>
       </c>
       <c r="R2" t="n">
-        <v>7241443</v>
+        <v>7241695</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252036</v>
+        <v>121252044</v>
       </c>
       <c r="B3" t="n">
-        <v>79594</v>
+        <v>91996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>780412</v>
+        <v>780241</v>
       </c>
       <c r="R3" t="n">
-        <v>7241695</v>
+        <v>7241838</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252047</v>
+        <v>121252037</v>
       </c>
       <c r="B4" t="n">
-        <v>91996</v>
+        <v>78346</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780452</v>
+        <v>780297</v>
       </c>
       <c r="R4" t="n">
-        <v>7241612</v>
+        <v>7241876</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252037</v>
+        <v>121252030</v>
       </c>
       <c r="B5" t="n">
-        <v>78346</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,34 +997,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780297</v>
+        <v>780156</v>
       </c>
       <c r="R5" t="n">
-        <v>7241876</v>
+        <v>7241427</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,6 +1065,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252035</v>
+        <v>121252032</v>
       </c>
       <c r="B6" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,16 +1112,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780451</v>
+        <v>780074</v>
       </c>
       <c r="R6" t="n">
-        <v>7241569</v>
+        <v>7241491</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252032</v>
+        <v>121252035</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,16 +1222,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1244,7 +1244,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780074</v>
+        <v>780451</v>
       </c>
       <c r="R7" t="n">
-        <v>7241491</v>
+        <v>7241569</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252033</v>
+        <v>121252047</v>
       </c>
       <c r="B8" t="n">
-        <v>57509</v>
+        <v>91996</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780312</v>
+        <v>780452</v>
       </c>
       <c r="R8" t="n">
-        <v>7241400</v>
+        <v>7241612</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252030</v>
+        <v>121252043</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>82393</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,42 +1434,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780156</v>
+        <v>780453</v>
       </c>
       <c r="R9" t="n">
-        <v>7241427</v>
+        <v>7241681</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,11 +1494,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121252041</v>
+        <v>121252045</v>
       </c>
       <c r="B10" t="n">
-        <v>78345</v>
+        <v>91996</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,25 +1532,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780441</v>
+        <v>780443</v>
       </c>
       <c r="R10" t="n">
-        <v>7241547</v>
+        <v>7241811</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121252040</v>
+        <v>121252031</v>
       </c>
       <c r="B11" t="n">
-        <v>78345</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,34 +1638,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>780431</v>
+        <v>780129</v>
       </c>
       <c r="R11" t="n">
-        <v>7241554</v>
+        <v>7241443</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,6 +1706,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1737,10 +1737,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121252042</v>
+        <v>121252046</v>
       </c>
       <c r="B12" t="n">
-        <v>90738</v>
+        <v>91996</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1749,25 +1749,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780388</v>
+        <v>780408</v>
       </c>
       <c r="R12" t="n">
-        <v>7241696</v>
+        <v>7241743</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121252046</v>
+        <v>121252033</v>
       </c>
       <c r="B13" t="n">
-        <v>91996</v>
+        <v>57509</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1851,25 +1851,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780408</v>
+        <v>780312</v>
       </c>
       <c r="R13" t="n">
-        <v>7241743</v>
+        <v>7241400</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121252039</v>
+        <v>121252041</v>
       </c>
       <c r="B14" t="n">
-        <v>78346</v>
+        <v>78345</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1957,21 +1957,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1981,10 +1981,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780459</v>
+        <v>780441</v>
       </c>
       <c r="R14" t="n">
-        <v>7241605</v>
+        <v>7241547</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2043,10 +2043,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121252043</v>
+        <v>121252042</v>
       </c>
       <c r="B15" t="n">
-        <v>82393</v>
+        <v>90738</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>780453</v>
+        <v>780388</v>
       </c>
       <c r="R15" t="n">
-        <v>7241681</v>
+        <v>7241696</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121252044</v>
+        <v>121252040</v>
       </c>
       <c r="B16" t="n">
-        <v>91996</v>
+        <v>78345</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2157,25 +2157,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>780241</v>
+        <v>780431</v>
       </c>
       <c r="R16" t="n">
-        <v>7241838</v>
+        <v>7241554</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121252034</v>
+        <v>121252039</v>
       </c>
       <c r="B17" t="n">
-        <v>57372</v>
+        <v>78346</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,42 +2263,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>780223</v>
+        <v>780459</v>
       </c>
       <c r="R17" t="n">
-        <v>7241946</v>
+        <v>7241605</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,11 +2323,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2362,10 +2349,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121252045</v>
+        <v>121252034</v>
       </c>
       <c r="B18" t="n">
-        <v>91996</v>
+        <v>57372</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2374,38 +2361,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780443</v>
+        <v>780223</v>
       </c>
       <c r="R18" t="n">
-        <v>7241811</v>
+        <v>7241946</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,6 +2433,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252036</v>
+        <v>121252041</v>
       </c>
       <c r="B2" t="n">
-        <v>79594</v>
+        <v>78345</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>780412</v>
+        <v>780441</v>
       </c>
       <c r="R2" t="n">
-        <v>7241695</v>
+        <v>7241547</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252044</v>
+        <v>121252045</v>
       </c>
       <c r="B3" t="n">
         <v>91996</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>780241</v>
+        <v>780443</v>
       </c>
       <c r="R3" t="n">
-        <v>7241838</v>
+        <v>7241811</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252037</v>
+        <v>121252047</v>
       </c>
       <c r="B4" t="n">
-        <v>78346</v>
+        <v>91996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780297</v>
+        <v>780452</v>
       </c>
       <c r="R4" t="n">
-        <v>7241876</v>
+        <v>7241612</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252030</v>
+        <v>121252035</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,16 +997,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780156</v>
+        <v>780451</v>
       </c>
       <c r="R5" t="n">
-        <v>7241427</v>
+        <v>7241569</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,11 +1065,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252032</v>
+        <v>121252042</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,42 +1107,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780074</v>
+        <v>780388</v>
       </c>
       <c r="R6" t="n">
-        <v>7241491</v>
+        <v>7241696</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252035</v>
+        <v>121252032</v>
       </c>
       <c r="B7" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,16 +1209,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1244,7 +1231,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1254,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780451</v>
+        <v>780074</v>
       </c>
       <c r="R7" t="n">
-        <v>7241569</v>
+        <v>7241491</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1303,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252047</v>
+        <v>121252033</v>
       </c>
       <c r="B8" t="n">
-        <v>91996</v>
+        <v>57509</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1315,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780452</v>
+        <v>780312</v>
       </c>
       <c r="R8" t="n">
-        <v>7241612</v>
+        <v>7241400</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252043</v>
+        <v>121252034</v>
       </c>
       <c r="B9" t="n">
-        <v>82393</v>
+        <v>57372</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,34 +1421,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780453</v>
+        <v>780223</v>
       </c>
       <c r="R9" t="n">
-        <v>7241681</v>
+        <v>7241946</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,6 +1489,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1520,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121252045</v>
+        <v>121252040</v>
       </c>
       <c r="B10" t="n">
-        <v>91996</v>
+        <v>78345</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,25 +1532,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780443</v>
+        <v>780431</v>
       </c>
       <c r="R10" t="n">
-        <v>7241811</v>
+        <v>7241554</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121252031</v>
+        <v>121252044</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>91996</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,46 +1634,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>780129</v>
+        <v>780241</v>
       </c>
       <c r="R11" t="n">
-        <v>7241443</v>
+        <v>7241838</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,11 +1698,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1737,10 +1724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121252046</v>
+        <v>121252037</v>
       </c>
       <c r="B12" t="n">
-        <v>91996</v>
+        <v>78346</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1749,25 +1736,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1777,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780408</v>
+        <v>780297</v>
       </c>
       <c r="R12" t="n">
-        <v>7241743</v>
+        <v>7241876</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121252033</v>
+        <v>121252036</v>
       </c>
       <c r="B13" t="n">
-        <v>57509</v>
+        <v>79594</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1851,25 +1838,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1879,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780312</v>
+        <v>780412</v>
       </c>
       <c r="R13" t="n">
-        <v>7241400</v>
+        <v>7241695</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1941,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121252041</v>
+        <v>121252039</v>
       </c>
       <c r="B14" t="n">
-        <v>78345</v>
+        <v>78346</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1957,21 +1944,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1981,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780441</v>
+        <v>780459</v>
       </c>
       <c r="R14" t="n">
-        <v>7241547</v>
+        <v>7241605</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2043,10 +2030,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121252042</v>
+        <v>121252030</v>
       </c>
       <c r="B15" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2059,34 +2046,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>780388</v>
+        <v>780156</v>
       </c>
       <c r="R15" t="n">
-        <v>7241696</v>
+        <v>7241427</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2119,6 +2114,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2145,10 +2145,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121252040</v>
+        <v>121252031</v>
       </c>
       <c r="B16" t="n">
-        <v>78345</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2161,34 +2161,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>780431</v>
+        <v>780129</v>
       </c>
       <c r="R16" t="n">
-        <v>7241554</v>
+        <v>7241443</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2221,6 +2229,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2247,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121252039</v>
+        <v>121252043</v>
       </c>
       <c r="B17" t="n">
-        <v>78346</v>
+        <v>82393</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2287,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>780459</v>
+        <v>780453</v>
       </c>
       <c r="R17" t="n">
-        <v>7241605</v>
+        <v>7241681</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2349,10 +2362,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121252034</v>
+        <v>121252046</v>
       </c>
       <c r="B18" t="n">
-        <v>57372</v>
+        <v>91996</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2361,46 +2374,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780223</v>
+        <v>780408</v>
       </c>
       <c r="R18" t="n">
-        <v>7241946</v>
+        <v>7241743</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2433,11 +2438,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252041</v>
+        <v>121252045</v>
       </c>
       <c r="B2" t="n">
-        <v>78345</v>
+        <v>91996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>780441</v>
+        <v>780443</v>
       </c>
       <c r="R2" t="n">
-        <v>7241547</v>
+        <v>7241811</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252045</v>
+        <v>121252041</v>
       </c>
       <c r="B3" t="n">
-        <v>91996</v>
+        <v>78345</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>780443</v>
+        <v>780441</v>
       </c>
       <c r="R3" t="n">
-        <v>7241811</v>
+        <v>7241547</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -2467,7 +2467,7 @@
         <v>121252029</v>
       </c>
       <c r="B19" t="n">
-        <v>91049</v>
+        <v>91059</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -675,50 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252045</v>
+        <v>121252029</v>
       </c>
       <c r="B2" t="n">
-        <v>91996</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>71</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fomitopsis infirma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>780443</v>
+        <v>780314</v>
       </c>
       <c r="R2" t="n">
-        <v>7241811</v>
+        <v>7241830</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,11 +751,21 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2024-12-04 Nu mikroskoperad av Mikael Gudrunsson, urskogsporing stämmer!  2024-11-17 Ska mikroskoperas, men tycker det stämmer makroskopiskt med de karaktärer jag kunnat hitta i både bestämningslitteratur och råd från kunniga. Porerna går hela vägen ut i kanten, den är mjuk (kändes "fluffig" i färskt tillstånd och nu då den är torkad är den mycket spröd och blir snabbt till pulver om man rullar den mellan fingrarna. Upplever den inte alls seg.), fäster rätt hårt i underlaget men inte stenhårt, är ungefär 5mm tjock, 3-4 porer/mm (17-19/5mm) med enskilda större porer insprängda, på mycket grov kolad tallåga tätt tryckt mot marken. Området mycket tydligt präglad av brand, bränd silverved av tall i olika dimensioner fanns genomgående spritt i området.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -777,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252041</v>
+        <v>121252043</v>
       </c>
       <c r="B3" t="n">
-        <v>78345</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +796,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>780441</v>
+        <v>780453</v>
       </c>
       <c r="R3" t="n">
-        <v>7241547</v>
+        <v>7241681</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,19 +882,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252047</v>
+        <v>121252044</v>
       </c>
       <c r="B4" t="n">
-        <v>91996</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -919,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780452</v>
+        <v>780241</v>
       </c>
       <c r="R4" t="n">
-        <v>7241612</v>
+        <v>7241838</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252035</v>
+        <v>121252045</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,42 +990,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780451</v>
+        <v>780443</v>
       </c>
       <c r="R5" t="n">
-        <v>7241569</v>
+        <v>7241811</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,15 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252042</v>
+        <v>121252046</v>
       </c>
       <c r="B6" t="n">
-        <v>90738</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1107,21 +1087,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1131,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>780388</v>
+        <v>780408</v>
       </c>
       <c r="R6" t="n">
-        <v>7241696</v>
+        <v>7241743</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,15 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252032</v>
+        <v>121252047</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1209,42 +1184,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780074</v>
+        <v>780452</v>
       </c>
       <c r="R7" t="n">
-        <v>7241491</v>
+        <v>7241612</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,15 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252033</v>
+        <v>121252040</v>
       </c>
       <c r="B8" t="n">
-        <v>57509</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1319,21 +1281,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1343,10 +1305,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780312</v>
+        <v>780431</v>
       </c>
       <c r="R8" t="n">
-        <v>7241400</v>
+        <v>7241554</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,15 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252034</v>
+        <v>121252041</v>
       </c>
       <c r="B9" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1421,42 +1378,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780223</v>
+        <v>780441</v>
       </c>
       <c r="R9" t="n">
-        <v>7241946</v>
+        <v>7241547</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,11 +1438,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1520,37 +1464,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121252040</v>
+        <v>121252036</v>
       </c>
       <c r="B10" t="n">
-        <v>78345</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1560,10 +1499,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780431</v>
+        <v>780412</v>
       </c>
       <c r="R10" t="n">
-        <v>7241554</v>
+        <v>7241695</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,15 +1561,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121252044</v>
+        <v>121252034</v>
       </c>
       <c r="B11" t="n">
-        <v>91996</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1638,34 +1572,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>780241</v>
+        <v>780223</v>
       </c>
       <c r="R11" t="n">
-        <v>7241838</v>
+        <v>7241946</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,6 +1640,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,50 +1671,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121252037</v>
+        <v>121252035</v>
       </c>
       <c r="B12" t="n">
-        <v>78346</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780297</v>
+        <v>780451</v>
       </c>
       <c r="R12" t="n">
-        <v>7241876</v>
+        <v>7241569</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,50 +1776,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121252036</v>
+        <v>121252030</v>
       </c>
       <c r="B13" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780412</v>
+        <v>780156</v>
       </c>
       <c r="R13" t="n">
-        <v>7241695</v>
+        <v>7241427</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,6 +1855,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,15 +1886,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121252039</v>
+        <v>121252031</v>
       </c>
       <c r="B14" t="n">
-        <v>78346</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,34 +1897,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>780459</v>
+        <v>780129</v>
       </c>
       <c r="R14" t="n">
-        <v>7241605</v>
+        <v>7241443</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,6 +1965,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2030,15 +1996,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121252030</v>
+        <v>121252032</v>
       </c>
       <c r="B15" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2068,7 +2029,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2078,10 +2039,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>780156</v>
+        <v>780074</v>
       </c>
       <c r="R15" t="n">
-        <v>7241427</v>
+        <v>7241491</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2114,11 +2075,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2145,15 +2101,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121252031</v>
+        <v>121252033</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2161,42 +2112,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>780129</v>
+        <v>780312</v>
       </c>
       <c r="R16" t="n">
-        <v>7241443</v>
+        <v>7241400</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,11 +2172,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,15 +2198,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121252043</v>
+        <v>121252037</v>
       </c>
       <c r="B17" t="n">
-        <v>82393</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,21 +2209,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2233,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>780453</v>
+        <v>780297</v>
       </c>
       <c r="R17" t="n">
-        <v>7241681</v>
+        <v>7241876</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2362,37 +2295,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121252046</v>
+        <v>121252038</v>
       </c>
       <c r="B18" t="n">
-        <v>91996</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2402,10 +2330,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780408</v>
+        <v>780455</v>
       </c>
       <c r="R18" t="n">
-        <v>7241743</v>
+        <v>7241619</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2464,53 +2392,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121252029</v>
+        <v>121252039</v>
       </c>
       <c r="B19" t="n">
-        <v>91059</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>71</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Trutmyran, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>780314</v>
+        <v>780459</v>
       </c>
       <c r="R19" t="n">
-        <v>7241830</v>
+        <v>7241605</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,21 +2465,11 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2024-12-04 Nu mikroskoperad av Mikael Gudrunsson, urskogsporing stämmer!  2024-11-17 Ska mikroskoperas, men tycker det stämmer makroskopiskt med de karaktärer jag kunnat hitta i både bestämningslitteratur och råd från kunniga. Porerna går hela vägen ut i kanten, den är mjuk (kändes "fluffig" i färskt tillstånd och nu då den är torkad är den mycket spröd och blir snabbt till pulver om man rullar den mellan fingrarna. Upplever den inte alls seg.), fäster rätt hårt i underlaget men inte stenhårt, är ungefär 5mm tjock, 3-4 porer/mm (17-19/5mm) med enskilda större porer insprängda, på mycket grov kolad tallåga tätt tryckt mot marken. Området mycket tydligt präglad av brand, bränd silverved av tall i olika dimensioner fanns genomgående spritt i området.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG19" t="b">
         <v>0</v>

--- a/artfynd/A 50032-2024 artfynd.xlsx
+++ b/artfynd/A 50032-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252029</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252043</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252044</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1073,6 +1093,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252045</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1170,6 +1195,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252046</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1267,6 +1297,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252047</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1364,6 +1399,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252040</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1461,6 +1501,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252041</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1558,6 +1603,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252036</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1668,6 +1718,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252034</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1773,6 +1828,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252035</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1883,6 +1943,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252030</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1993,6 +2058,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252031</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2098,6 +2168,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252032</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2195,6 +2270,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252033</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2292,6 +2372,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252037</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252038</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2486,8 +2576,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252039</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>